--- a/products/manufacturing-templates/dist/Preventive-Maintenance-Schedule.xlsx
+++ b/products/manufacturing-templates/dist/Preventive-Maintenance-Schedule.xlsx
@@ -935,15 +935,15 @@
       </c>
       <c r="E5" s="14" t="n">
         <f aca="true">TODAY()-100</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="F5" s="15" t="n">
         <f aca="false">IF(OR(A5="",B5=""),"",IF(MAX(N(E5),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A5)*('Completion Log'!$C$5:$C$2004=B5)*'Completion Log'!$A$5:$A$2004)))=0,"",MAX(N(E5),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A5)*('Completion Log'!$C$5:$C$2004=B5)*'Completion Log'!$A$5:$A$2004)))))</f>
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="G5" s="15" t="n">
         <f aca="true">IF(OR(A5="",B5="",OR(NOT(ISNUMBER(C5)),N(C5)&lt;=0)),"",IF(F5="",TODAY(),F5+C5))</f>
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="H5" s="16" t="n">
         <f aca="true">IF(G5="","",G5-TODAY())</f>
@@ -972,15 +972,15 @@
       </c>
       <c r="E6" s="14" t="n">
         <f aca="true">TODAY()-3</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" s="15" t="n">
         <f aca="false">IF(OR(A6="",B6=""),"",IF(MAX(N(E6),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A6)*('Completion Log'!$C$5:$C$2004=B6)*'Completion Log'!$A$5:$A$2004)))=0,"",MAX(N(E6),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A6)*('Completion Log'!$C$5:$C$2004=B6)*'Completion Log'!$A$5:$A$2004)))))</f>
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="G6" s="15" t="n">
         <f aca="true">IF(OR(A6="",B6="",OR(NOT(ISNUMBER(C6)),N(C6)&lt;=0)),"",IF(F6="",TODAY(),F6+C6))</f>
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="H6" s="16" t="n">
         <f aca="true">IF(G6="","",G6-TODAY())</f>
@@ -1009,15 +1009,15 @@
       </c>
       <c r="E7" s="14" t="n">
         <f aca="true">TODAY()-27</f>
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F7" s="15" t="n">
         <f aca="false">IF(OR(A7="",B7=""),"",IF(MAX(N(E7),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A7)*('Completion Log'!$C$5:$C$2004=B7)*'Completion Log'!$A$5:$A$2004)))=0,"",MAX(N(E7),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A7)*('Completion Log'!$C$5:$C$2004=B7)*'Completion Log'!$A$5:$A$2004)))))</f>
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="G7" s="15" t="n">
         <f aca="true">IF(OR(A7="",B7="",OR(NOT(ISNUMBER(C7)),N(C7)&lt;=0)),"",IF(F7="",TODAY(),F7+C7))</f>
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="H7" s="16" t="n">
         <f aca="true">IF(G7="","",G7-TODAY())</f>
@@ -1047,11 +1047,11 @@
       <c r="E8" s="14"/>
       <c r="F8" s="15" t="n">
         <f aca="false">IF(OR(A8="",B8=""),"",IF(MAX(N(E8),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A8)*('Completion Log'!$C$5:$C$2004=B8)*'Completion Log'!$A$5:$A$2004)))=0,"",MAX(N(E8),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A8)*('Completion Log'!$C$5:$C$2004=B8)*'Completion Log'!$A$5:$A$2004)))))</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="G8" s="15" t="n">
         <f aca="true">IF(OR(A8="",B8="",OR(NOT(ISNUMBER(C8)),N(C8)&lt;=0)),"",IF(F8="",TODAY(),F8+C8))</f>
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="H8" s="16" t="n">
         <f aca="true">IF(G8="","",G8-TODAY())</f>
@@ -1080,15 +1080,15 @@
       </c>
       <c r="E9" s="14" t="n">
         <f aca="true">TODAY()-20</f>
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F9" s="15" t="n">
         <f aca="false">IF(OR(A9="",B9=""),"",IF(MAX(N(E9),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A9)*('Completion Log'!$C$5:$C$2004=B9)*'Completion Log'!$A$5:$A$2004)))=0,"",MAX(N(E9),SUMPRODUCT(MAX(('Completion Log'!$B$5:$B$2004=A9)*('Completion Log'!$C$5:$C$2004=B9)*'Completion Log'!$A$5:$A$2004)))))</f>
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="true">IF(OR(A9="",B9="",OR(NOT(ISNUMBER(C9)),N(C9)&lt;=0)),"",IF(F9="",TODAY(),F9+C9))</f>
-        <v>46465</v>
+        <v>46466</v>
       </c>
       <c r="H9" s="16" t="n">
         <f aca="true">IF(G9="","",G9-TODAY())</f>
@@ -8265,7 +8265,7 @@
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="n">
         <f aca="true">TODAY()-2</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="B5" s="9" t="s">
         <v>43</v>
